--- a/docs/templates/Шаблон_заявки_СпортДок_по_образцу_ПР.xlsx
+++ b/docs/templates/Шаблон_заявки_СпортДок_по_образцу_ПР.xlsx
@@ -1668,14 +1668,14 @@
         </is>
       </c>
       <c r="G4" s="231" t="inlineStr"/>
-      <c r="H4" s="232" t="n"/>
-      <c r="I4" s="232" t="n"/>
-      <c r="J4" s="232" t="n"/>
-      <c r="K4" s="232" t="n"/>
-      <c r="L4" s="232" t="n"/>
-      <c r="M4" s="232" t="n"/>
-      <c r="N4" s="232" t="n"/>
-      <c r="O4" s="232" t="n"/>
+      <c r="H4" s="219" t="n"/>
+      <c r="I4" s="219" t="n"/>
+      <c r="J4" s="219" t="n"/>
+      <c r="K4" s="219" t="n"/>
+      <c r="L4" s="219" t="n"/>
+      <c r="M4" s="219" t="n"/>
+      <c r="N4" s="219" t="n"/>
+      <c r="O4" s="219" t="n"/>
       <c r="P4" s="202" t="n"/>
       <c r="Q4" s="12" t="n"/>
       <c r="R4" s="12" t="n"/>
@@ -1746,22 +1746,22 @@
       </c>
       <c r="B6" s="234" t="inlineStr">
         <is>
+          <t>пол</t>
+        </is>
+      </c>
+      <c r="C6" s="234" t="inlineStr">
+        <is>
           <t>Фамилия</t>
         </is>
       </c>
-      <c r="C6" s="234" t="inlineStr">
+      <c r="D6" s="234" t="inlineStr">
         <is>
           <t>Имя</t>
         </is>
       </c>
-      <c r="D6" s="234" t="inlineStr">
+      <c r="E6" s="234" t="inlineStr">
         <is>
           <t>Отчество</t>
-        </is>
-      </c>
-      <c r="E6" s="234" t="inlineStr">
-        <is>
-          <t>пол</t>
         </is>
       </c>
       <c r="F6" s="234" t="inlineStr">
@@ -50471,19 +50471,19 @@
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="Q6:Q7"/>
     <mergeCell ref="I6:O6"/>
-    <mergeCell ref="Q6:Q7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="G4:O4"/>
-    <mergeCell ref="D6:D7"/>
     <mergeCell ref="I7:L7"/>
     <mergeCell ref="I5:P5"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
     <mergeCell ref="F6:F7"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="E8:E257" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Пол" error="Выберите м или ж" type="list">
+    <dataValidation sqref="B8:B257" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Пол" error="Выберите м или ж" type="list">
       <formula1>"м,ж"</formula1>
     </dataValidation>
     <dataValidation sqref="I8:L257" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Кумитэ" error="Выберите из списка" type="list">
